--- a/amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx
+++ b/amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx
@@ -4667,7 +4667,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5203,7 +5203,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5421,7 +5421,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5542,7 +5542,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5663,7 +5663,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5784,7 +5784,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5905,7 +5905,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6064,7 +6064,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6121,7 +6121,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6678,7 +6678,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6829,7 +6829,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -38022,7 +38022,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx
+++ b/amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx
@@ -6974,7 +6974,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6993,7 +6993,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -38041,7 +38041,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -38060,7 +38060,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx
+++ b/amkr/dist/20261025_艾克爾模型_v0.2.1.xlsx
@@ -4651,26 +4651,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5187,26 +5187,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5405,26 +5405,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5526,26 +5526,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5647,26 +5647,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5768,26 +5768,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5889,26 +5889,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6048,26 +6048,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6105,26 +6105,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6662,26 +6662,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6813,26 +6813,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -38262,26 +38262,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
